--- a/docs/templates/customer_import_test_data.xlsx
+++ b/docs/templates/customer_import_test_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="客户导入" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户导入" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户导入'!$A$1:$S$1</definedName>
@@ -854,25 +854,19 @@
           <t>新客户，需求还在确认</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>48</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>竞争环境较好</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>76</v>
-      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>暂未建立关键人关系</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>30</v>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>先完成需求澄清</t>
@@ -883,7 +877,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>样例客户：无联系人行</t>
+          <t>样例客户：无评分无联系人行</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
@@ -990,7 +984,7 @@
     <dataValidation sqref="S2:S5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否,Y,N,true,false,1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G5000 I2:I5000 K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">
+    <dataValidation sqref="G2:G5000 I2:I5000 K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
